--- a/AAII_Financials/Quarterly/APD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APD_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3161000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3171800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3102500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3166900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3022700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2916200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2931500</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2985500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2930200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2997400</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3033900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3200100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3174700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3570000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3189300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2945100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2994200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2841100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2604700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2502000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2375200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2320100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2065200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2216300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2254700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2283200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2224000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2187700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2224000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2298900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2155700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2216600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2203100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2121900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1980100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1882500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1945500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2125000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2184400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2107500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2145500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2040100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2053900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2016500</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2005600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1991500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2067200</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2070700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2282800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2272300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2621200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2342100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2151600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2223600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2006300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1801900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1745500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1632400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1566500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1344900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1460100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1490800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1466000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1474700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1565800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1545400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1506500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1571800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1545000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1486000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1403800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1318100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1347500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1036000</v>
+      </c>
+      <c r="E10" s="3">
         <v>987400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>995000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1021400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>982600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>862300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>915000</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>979900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>938700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>930200</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>963200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>917300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>902400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>948800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>847200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>793500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>770600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>834800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>802800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>756500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>742800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>753600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>720300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>756200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>768100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>792400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>758000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>713000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>680000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>733100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>713600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>649200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>644800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>658100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>635900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>576300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>564400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E12" s="3">
         <v>21600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22000</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>27000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25700</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>31100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>25700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>23500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>27100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>19900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>19200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>17700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>22900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>18100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>16900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>15000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>20400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>14500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>14600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>13200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>14600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>14800</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>15100</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,104 +1496,107 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2907400</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="F14" s="3">
-        <v>-2827400</v>
+        <v>22000</v>
       </c>
       <c r="G14" s="3">
+        <v>795900</v>
+      </c>
+      <c r="H14" s="3">
         <v>-74200</v>
       </c>
-      <c r="H14" s="3">
-        <v>29800</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>35</v>
+      <c r="I14" s="3">
+        <v>2957700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>57000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P14" s="3">
         <v>59300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>185600</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>73700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>23200</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-33800</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>25500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>29000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1587,67 +1607,70 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>49300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>210300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>14400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>80200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>52400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>385400</v>
+      </c>
+      <c r="E15" s="3">
         <v>375000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>370700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>412800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>401000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>383600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>366800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>380800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>360300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>360800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>349200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>357300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>339900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>339600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2353800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2423400</v>
       </c>
-      <c r="E17" s="3">
-        <v>2371200</v>
-      </c>
       <c r="F17" s="3">
-        <v>5990800</v>
+        <v>2349200</v>
       </c>
       <c r="G17" s="3">
+        <v>2367500</v>
+      </c>
+      <c r="H17" s="3">
         <v>2288300</v>
       </c>
-      <c r="H17" s="3">
-        <v>5226200</v>
-      </c>
       <c r="I17" s="3">
+        <v>2298300</v>
+      </c>
+      <c r="J17" s="3">
         <v>2272500</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2275000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2264100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2352300</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2352400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2577100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2522700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2943500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2561900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2383200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2471200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2224400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2027600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1953500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1836100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1759900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1526000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1639100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1693700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1680000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1654300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1671200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1769000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1765200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1743200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1700300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1755900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1745700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1863200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1584500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1554400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1561400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>807200</v>
+      </c>
+      <c r="E18" s="3">
         <v>748400</v>
       </c>
-      <c r="E18" s="3">
-        <v>731300</v>
-      </c>
       <c r="F18" s="3">
-        <v>-2823900</v>
+        <v>753300</v>
       </c>
       <c r="G18" s="3">
+        <v>799400</v>
+      </c>
+      <c r="H18" s="3">
         <v>734400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2310000</v>
-      </c>
       <c r="I18" s="3">
+        <v>617900</v>
+      </c>
+      <c r="J18" s="3">
         <v>659000</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>710500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>666100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>645100</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>681500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>623000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>652000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>626500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>627400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>561900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>523000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>616700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>577100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>548500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>539100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>560200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>539200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>577200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>561000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>603200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>569700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>516500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>455000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>533700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>515800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>455400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>460700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>457400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>258700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>395600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>328100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>384100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-211900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-185900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-172100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-185800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-143700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-150200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-135300</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-186200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-162200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-165400</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-175300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-174400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>109400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>117000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>126600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>129900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>170400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>109000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>84300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>86600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>87900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>73600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>59300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>95300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>67300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>76500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>76000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>59900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>74000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>29400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>51200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>20400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>50400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-33800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>36700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>28900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>69900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1404500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1309300</v>
       </c>
-      <c r="E21" s="3">
-        <v>1274100</v>
-      </c>
       <c r="F21" s="3">
-        <v>-2225300</v>
+        <v>1296100</v>
       </c>
       <c r="G21" s="3">
+        <v>1398000</v>
+      </c>
+      <c r="H21" s="3">
         <v>1279100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-1776200</v>
-      </c>
       <c r="I21" s="3">
+        <v>1151700</v>
+      </c>
+      <c r="J21" s="3">
         <v>1161100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>380800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1257000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1189100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1159700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>357300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1196700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1082900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1076300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1091200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1027700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1025700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1058300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>997100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>964400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>950700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>944300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>889100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>967200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>917500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>973300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>914800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>838500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>787000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>820300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>830200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>746600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>709000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>738800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>441800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>644100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>563100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>666500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E22" s="3">
         <v>49500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>52600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>68000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>61500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>53700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3800</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>59900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>53500</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>41200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>32500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>32300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>30500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>33400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>35600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>36100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>36700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>39200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>32100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>18700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>29800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>36200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>35400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>39900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>34200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>32800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>26800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>26600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>28600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>29200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>27700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>20400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>62800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1937700</v>
+      </c>
+      <c r="E23" s="3">
         <v>883500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>850800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>121300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>890800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2243300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>790500</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>849500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>711400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>757000</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>750100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>570900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>720200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>711000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>721300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>659500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>662900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>692300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>625800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>599000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>590300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>594600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>566400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>653200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>609600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>649900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>609500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>541000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>489100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>528900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>551800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>479800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>454500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>479200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>195700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>404600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>336600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>391200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-515400</v>
+      </c>
+      <c r="E24" s="3">
         <v>158700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>159400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>111200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>159600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-505800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>140700</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>130500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>135400</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>139600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>121000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>136400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>130600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>134200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>122700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>113300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>125300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>101700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>121900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>113900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>99900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>109300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>148500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>120700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>131200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>106100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>107500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>147700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>38900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>107100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>56200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>85300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>89300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>94500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>78400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>96800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-1422300</v>
+      </c>
+      <c r="E26" s="3">
         <v>724800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>691400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>731200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1737500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>649800</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>708900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>580900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>621600</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>610500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>449900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>583800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>580400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>587100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>536800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>549600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>567000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>524100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>477100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>476400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>494700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>457100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>504700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>488900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>518700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>503400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>433500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>341400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>490000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>444700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>423600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>369200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>480500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>106400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>310100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>258200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>294400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-1440800</v>
+      </c>
+      <c r="E27" s="3">
         <v>710400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>678200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>713800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1730600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>617400</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>696600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>572400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>609300</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>595600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>439800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>572200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>570500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>582100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>530500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>560400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>558600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>525400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>473100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>471700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>486800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>446500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>492100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>475600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>503200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>491200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>421300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>331900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>483200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>430700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>416400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>362100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>474200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>104200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>304400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>251600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>295400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3165,11 +3226,11 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-8000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
@@ -3194,15 +3255,15 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>12600</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
@@ -3210,70 +3271,73 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>51800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>8200</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>10300</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>15600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-30300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-207500</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-5500</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-2300</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>1825600</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>48200</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>90600</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E32" s="3">
         <v>185900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>172100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>185800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>143700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>150200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>135300</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>186200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>162200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>165400</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>175300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>174400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-109400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-117000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-126600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-129900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-170400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-109000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-84300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-86600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-87900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-73600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-59300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-95300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-67300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-76500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-29400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-68800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-51200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-20400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-50400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>33800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-36700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-28900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-69900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-1440800</v>
+      </c>
+      <c r="E33" s="3">
         <v>710400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>678200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>713800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1730600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>617400</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>696600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>572400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>609300</v>
       </c>
-      <c r="N33" s="3" t="s">
+      <c r="O33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>595600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>439800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>572200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>583100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>582100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>530500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>560400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>610400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>533600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>473100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>482000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>486800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>446500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>477800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>475600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>503200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>488000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>421300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>347500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>452900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>473900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>416400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>154600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>468700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>101900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2130000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>299800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>386000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-1440800</v>
+      </c>
+      <c r="E35" s="3">
         <v>710400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>678200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>713800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1730600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>617400</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>696600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>572400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>609300</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>595600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>439800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>572200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>583100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>582100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>530500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>560400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>610400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>533600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>473100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>482000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>486800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>446500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>477800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>475600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>503200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>488000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>421300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>347500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>452900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>473900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>416400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>154600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>468700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>101900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2130000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>299800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>386000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>980500</v>
+      </c>
+      <c r="E41" s="3">
         <v>951000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1026400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1856000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2324300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1491400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1845500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2979700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2375700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2535000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1962600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1617000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1637700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2242400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3131000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2711000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2957400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2348700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2953700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4468900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4291600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5786300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5788000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5253000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3921400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2220100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2406100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2248700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2696800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2735900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2923300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2791300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2986500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3066900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2722600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3273600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2332600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1869300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>655500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1293200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E42" s="3">
         <v>3200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>116700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>122300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>111400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>280900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>349100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>285900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>280000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>19600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>590700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>357600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>848900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>728600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1331900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1524900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>409200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>412000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1104900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2515700</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>166000</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
       <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>2600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>12300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>184700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>137000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>407100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>404000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1016100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1423200</v>
-      </c>
-      <c r="AO42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="AP42" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2439800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2505400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2492800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2346600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2549400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2406500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2270900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2168200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2149700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2253500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2328900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2162700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2398500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2136800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2012600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1878500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1923000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2011600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1878200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1696200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1681900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1612200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1625500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1274800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1409700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1399400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1288600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1260200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1340700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1258500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1268200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1207200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1227600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1531200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1537100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1577300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1396600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1444100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1361100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1515100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>751600</v>
+      </c>
+      <c r="E44" s="3">
         <v>767900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>788100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>776500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>797700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>769700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>739000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>766000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>755600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>721200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>709300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>651800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>663900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>645600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>635300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>514200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>514000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>507500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>487200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>453900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>447200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>430300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>422900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>404800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>410900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>399700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>400600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>388300</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>408300</v>
       </c>
       <c r="AF44" s="3">
         <v>408300</v>
       </c>
       <c r="AG44" s="3">
+        <v>408300</v>
+      </c>
+      <c r="AH44" s="3">
         <v>403400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>473600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>416000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>438400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>432800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>420200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>376600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>391600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>415300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>319600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>617000</v>
+      </c>
+      <c r="E45" s="3">
         <v>613900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>626600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>658700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>235400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>141700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>172200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>261300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>153200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>172900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>161000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>242900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>188800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>192100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>522600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>588500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>615300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>532700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>435800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>425400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>431200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>528600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>561400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>647400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>748800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>669300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>624400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>555100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>469400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>489900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>482700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>425400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>418100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>222800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>255900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>201600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>225100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>165900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1116900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1189400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4963500</v>
+      </c>
+      <c r="E46" s="3">
         <v>5012600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5103200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5825800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6147600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5187600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5351700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6363000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5677400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6057300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5649500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5200500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5354000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5721600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6321100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6282900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6367300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6249400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6483500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>8376300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8376800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8766600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8809800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8684900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9006500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4688500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4719700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4618300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4915200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4895200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5089900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5082200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5055500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5396300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5355500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5876700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5347000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5294100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3548800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4317300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5836500</v>
+      </c>
+      <c r="E47" s="3">
         <v>5657300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5651000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5533500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5398300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5311000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5038600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4898500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4941100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4943300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4750500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4985500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4518600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4427100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3970800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3936900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3981400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4116100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4053500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2389600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2341500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2327400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2336600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2248500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2166700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2155400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2223100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2166200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2228800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2254000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2228300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2290500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2317500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2434100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2384000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2418700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2384000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2444200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2417300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2505300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25785700</v>
+      </c>
+      <c r="E48" s="3">
         <v>27611500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27067300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26281800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26616900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25003700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25748200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24418600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22464200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20999300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19914300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18446100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17483600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16465300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15794000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14160500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14131700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14095200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13624700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13254600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13035600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12628300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12517100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12341500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11820900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10974800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10692200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10337600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10427600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10193800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9959800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9923700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9902000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8817700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8631900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8440200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8317000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8198200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8030300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8259700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1235800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1242200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1265900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1257400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1272100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1168700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1154000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1216700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1189500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1201600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1238500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1196300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1250500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1251100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1239400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1170500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1243600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1332000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1342100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1332200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1375500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1363800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1376400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1327300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1180200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1163200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1232000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1216600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1261500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1230500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1197300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1227400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1243100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1259400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1219900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1089800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1068900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1204800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1187800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1233000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2198700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1688100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1714100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1606100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1852200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1825100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2053000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1823900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2264900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2261600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2079500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1258100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1802800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1008600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>953000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1641800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1765000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1657000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1621500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1506500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1122700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1072800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1048200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>566300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>607800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>519300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>784600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>604100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>698800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>671000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>666700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>654500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>687900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>603600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>617500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>641800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>736900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>730200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>772000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1713300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40445600</v>
+      </c>
+      <c r="E54" s="3">
         <v>41644700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41240700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41059500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41659100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38872900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40017200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39574600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36974300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35921700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34118200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32002500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30929500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29435400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28278300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27192600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27489000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27449700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27125300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26859200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26252100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26158900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>26088100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25168500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24782100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19501200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19651600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18942800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19531900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19244500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19142000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19178300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19206000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18511100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18208800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>18467200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>17853800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>17871500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15956200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>18028600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,8 +6145,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6026,11 +6157,11 @@
       <c r="E57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="3">
         <v>1437000</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>35</v>
@@ -6038,11 +6169,11 @@
       <c r="I57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57" s="3">
         <v>1451600</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>35</v>
@@ -6050,705 +6181,723 @@
       <c r="M57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O57" s="3">
         <v>1212900</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" s="3">
         <v>2127400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2332500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2067300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1841300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1791200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1851500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1671200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1629200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1528200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1762500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1601100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1521200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1579500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1544500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1496900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1460000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1708000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1763600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1910100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1494800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1541700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1814300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1466000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1400400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1485600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1578700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>930100</v>
+      </c>
+      <c r="E58" s="3">
         <v>489900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>240600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>843100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1237200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1607500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1204800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>796400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1150000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1121800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>234600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>969200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>776900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>182900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>565000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>559000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>754600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>693400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>199700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>486900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>499900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>888500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>915300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>477700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>838900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>67400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>75600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>98600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>546400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>488600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>453300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>460900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>95400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>124100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>98400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>560400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>559400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>542800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1029400</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1301200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3645200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3023400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3257300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1379000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3522400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3603100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3604600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1508500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3324500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2939200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2884600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1313300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3170800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2615000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>584500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>574300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>585000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>670400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>639200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>460700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>526000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>499700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>542400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>176500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>151000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>218300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>163900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>177800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>111900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>124400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>142200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>113800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>104300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>133400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>191500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>114300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>407800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>659100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>414800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>403200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4575300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3513300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3497900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4218600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4759600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5210600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4809400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4179600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4474500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4061000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3119200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3895800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3947700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2797900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3276900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3465800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3406900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3205100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2630100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2799100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2697100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3017400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2985900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2416700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2591000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1806900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1819000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1820900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2155200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2073000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2303500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2338300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2109800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1752300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1831600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2489000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2433200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2602300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2929800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3283100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17341100</v>
+      </c>
+      <c r="E61" s="3">
         <v>17952300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17951700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17587200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17133200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14924900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13969100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14251100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13584500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13217200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12568500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10149400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9333300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9675300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7492800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7085800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6831600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6748100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7178300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7150300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7166200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7115900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7091600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7430100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7358800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3245200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3265600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3227400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3273300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3302200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3314600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3351700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3775800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3442400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3414900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3402400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3366600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3300400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3289000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3909700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1015800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1012600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1010300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>769600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1037200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1007200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1021800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>775300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>914200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>894200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>920700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>691500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>929900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>916100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2991200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2938600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3034800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2985800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2941300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2821800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2897200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2890800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2938700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2878600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2808900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2725400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2637200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2506200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2376800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2365900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2320500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2312000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2510400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2623200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2641100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2390300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2544100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2548600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2476300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3622400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23849200</v>
+      </c>
+      <c r="E66" s="3">
         <v>23494900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23403600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23709700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23891100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22093300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21278500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20900900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20287300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19586800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17989100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16342200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15558800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14745200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14342600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14048600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13845100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13494600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13300200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13319500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13169200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13432700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13404500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13088700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13122800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8129300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8095600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7889200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8145800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8078800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8259100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8320800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8720000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7930300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7993500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8381000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8441400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8554100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8794700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>10949000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16299500</v>
+      </c>
+      <c r="E72" s="3">
         <v>18144200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17838000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17558600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17952900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17637300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19767300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19545700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17989900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17690000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17510000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17289700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16986900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16781300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16731400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16520300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16297900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16075900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15905200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15678300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15400200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15200000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15060500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14875700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14686600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14537200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14356900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14138400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13891900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13662000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13497900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13409900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13200200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12966500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12792300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>12846600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>12584200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>12692500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>10771700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10475500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13883800</v>
+      </c>
+      <c r="E76" s="3">
         <v>15649900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15411300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15024900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15537500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14703400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16692300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17036500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15101300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14913400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14873000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14312900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14138000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14058300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13935700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13144000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13643900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13955100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13825100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13539700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13082900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12726200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12683600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12079800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11659300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11371900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11556000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11053600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11386100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11165700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10882900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10857500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10486000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10580800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10215300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10086200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9412400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9317400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7161500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7079600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-1440800</v>
+      </c>
+      <c r="E81" s="3">
         <v>710400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>678200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>713800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1730600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>617400</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>696600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>572400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>609300</v>
       </c>
-      <c r="N81" s="3" t="s">
+      <c r="O81" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>595600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>439800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>572200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>583100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>582100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>530500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>560400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>610400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>533600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>473100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>482000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>486800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>446500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>477800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>475600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>503200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>488000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>421300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>347500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>452900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>473900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>416400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>154600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>468700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>101900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2130000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>299800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>386000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E83" s="3">
         <v>383600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>366800</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>360300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>360800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>349200</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>339900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>339600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>321500</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>337200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>335900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>321500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>332800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>337200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>335900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>332300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>332600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>335700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>329300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>323700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>310500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>290600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>294700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>289200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>293600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>269100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>262100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>258000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>257200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>245600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>240000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>227900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>231000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>216900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>211800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>206100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>230500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1305200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1103700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>900700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1261200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>855800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>328100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>811700</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1261400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>801700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>626600</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>845400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>638700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>719300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1017000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>908200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>519800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>785200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>826300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>928600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>812300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>774700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1251500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>774700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>571500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>667000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>966500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>717600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>630600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>655200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>691400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>743500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>546000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>561000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>722500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>505000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-174300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>514700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>869300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-995700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1107600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1251200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1517700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1495800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1891500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2117600</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1606600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1669400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1445500</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1322400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1006900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-834200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-787400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-705500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-769800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-663800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-616400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-620000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-563600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-664200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-463800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1114600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-482900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-447700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-482100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-544100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-560100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-403400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-410300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-585600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-256600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-232900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-274600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-293000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-239200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-465300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-992700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1075900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1242900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1487700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1261600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2237300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2182100</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="K94" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1547800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1560400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1665600</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1923800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2219800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-256200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1013100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-208300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-916700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1719100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-414900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1734800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-601400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>18200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>770900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3624500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-445700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-260700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-677900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-553400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-655600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-226500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-609800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-491000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-41400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-484900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>393100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>141600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>2055700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-257500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-249600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E96" s="3">
         <v>398600</v>
-      </c>
-      <c r="E96" s="3">
-        <v>398400</v>
       </c>
       <c r="F96" s="3">
         <v>398400</v>
       </c>
       <c r="G96" s="3">
+        <v>398400</v>
+      </c>
+      <c r="H96" s="3">
         <v>398300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>393800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>393600</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>393500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>389000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>388900</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>388700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>359800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-359400</v>
       </c>
       <c r="R96" s="3">
         <v>-359400</v>
       </c>
       <c r="S96" s="3">
+        <v>-359400</v>
+      </c>
+      <c r="T96" s="3">
         <v>-359200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-332600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-332100</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-332000</v>
       </c>
       <c r="W96" s="3">
         <v>-332000</v>
       </c>
       <c r="X96" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-296500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-296200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-296000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-295900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-256000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-255700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-255600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-255300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-241600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-241500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-241200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-241100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-208000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-207500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-207000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-206900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-187100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-186900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-186300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-285300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-490100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-239100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1209200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1550900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>274200</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="K100" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>135200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1349700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1362800</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>495500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>689000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-85600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-188500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-200500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-585100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-217800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-699900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-196100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-307100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-720800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4543300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-267500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-270300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-709700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-201000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-170000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-262000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-282200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-174500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-641100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-186500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-192600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-687300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-905000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>379700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E101" s="3">
         <v>4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-38000</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="G101" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-18600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>21800</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-21800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>42500</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-64700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>42500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-61800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-64700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-16300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>11400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>49200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>30000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>21400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>7600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-14400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-47700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>14200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>14000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>11900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>9300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>8400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-16200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-75400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-829600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-468300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>832900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-354100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1134200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-159300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>572400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>345600</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-604700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-888600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>420000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-246400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>608700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-605000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1515200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>177300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1494700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>535000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1331600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1701300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-186000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>157400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-448100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-39100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-187400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>132000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-195200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-80400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>344300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-551000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>941000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>463300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1202500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-664000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>986500</v>
       </c>
     </row>
